--- a/daily_matches/job_matches_2026-05-16.xlsx
+++ b/daily_matches/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer (DFW Hybrid)</t>
+          <t>AI Software Engineer III- PySpark, Python, AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Redshift, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b6307f2370f7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, CI/CD</t>
+          <t>RAG, Data Lake, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Artificial Intelligence and Machine Learning</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>StarTech Career</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Glue, Data Lake, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Git, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,112 +566,112 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=1580b156a1f4735a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, FastAPI, Docker, CI/CD</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, XGBoost, Keras, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a562a45e7f71103</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -683,55 +683,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Product Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, XGBoost, S3, Redshift, Git, Databricks, Redshift, MongoDB, Tableau, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, AKS, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e33dc62bcab33a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Senior ML, MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, AKS, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=81caf831ffe6a0c4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, Git, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d4fd8d0fbbb3383</t>
+          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Copilot, Synapse, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Sr Engineer, Cloud Operations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sayers Technology</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Hugging Face, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada0cebda8c02e70</t>
+          <t>https://www.indeed.com/viewjob?jk=aa50b2c84ae8c7e4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>AI Engineer, RAG, S3, FastAPI, Terraform, PostgreSQL, Polars, Dask, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, AKS, CI/CD, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3677cf32b1561e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Science &amp; GenAI Research Intern - IGEN</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Cortex, MLflow, Git, Snowflake, Power BI, Python</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1338061f4d8bce</t>
+          <t>https://www.indeed.com/viewjob?jk=822d95b3cf3078d3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
+          <t>RAG, Synapse, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, Data Lake, Apache Airflow, CI/CD, Jenkins, Git, Snowflake, Redshift, Python, SQL</t>
+          <t>RAG, Synapse, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Software Development Engineer - Operations Improvement</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, AKS, Snowflake, BigQuery, Redshift, Tableau, Python</t>
+          <t>RAG, Git, Snowflake, MongoDB, Tableau, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=94f52913ae2298c2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Scientist Associate Sr - Consumer Bank Marketing Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Cortex, Git, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=dc8e95a50fd96f2a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>PREDICTIVE DATA ANALYST - EMERGENCY APPOINTMENT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>County of Los Angeles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Synapse, Git, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d9cad9422d13e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>GenAI Software Engineer, Professional (Risk Engineering &amp; Automation)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ac47fc7032d69a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Platform Architect (Teradyne, North Reading)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Copilot, Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f5ad030c15c2708</t>
+          <t>https://www.indeed.com/viewjob?jk=80d37f09dfebcd34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist (Remote)</t>
+          <t>DATA SCIENTIST - EMERGENCY APPOINTMENT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>County of Los Angeles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, Git, Databricks, Tableau, Power BI, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,777 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3649c54bb9add7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>EVgo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Polars, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b58362ce0fa2f56</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Back-End Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>State Farm</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2b1ecedbe0964a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Omniverse Development - CDH</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00ef332303c51ba2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Architect, Data Platform — AgentExchange</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cae59bd9f58aca4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NEOTAX</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Zuora</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, Kafka, MySQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90f546ca7d4bb9ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2741521a662649fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87888982a5bc4187</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f72fe1f2413bd3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=399e6d5db623d7ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=111487ca64c3cc5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8adb509052de0a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f11eab60972765a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Leasing</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Santa Barbara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2080159e608ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Intern</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sabre Systems</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Lexington Park, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Matplotlib, Seaborn, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed785131256b4df</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Digital Manufacturing &amp; Test Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Daimler Truck North America</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Mount Holly, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68c95b41d6ba1f1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Go Engineer (GenAI)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Factored</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Kafka, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02504574b48631f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AI Automation Developer II</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Yale New Haven Health</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Stratford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Fire and Police Pension Association of Colorado</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=038cb13224209716</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Prompt Engineering, MLflow, CI/CD, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b454f4170c11247</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, OpenCV, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=baa3b1b115721152</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Software Engineer - Master</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, BigQuery, R, Java</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2f04390f66a135</t>
+          <t>https://www.indeed.com/viewjob?jk=4b703cf71ca5ef4b</t>
         </is>
       </c>
     </row>
